--- a/artfynd/A 1830-2024 artfynd.xlsx
+++ b/artfynd/A 1830-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1830-2024 artfynd.xlsx
+++ b/artfynd/A 1830-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113702608</v>
       </c>
       <c r="B2" t="n">
-        <v>93206</v>
+        <v>93209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1830-2024 artfynd.xlsx
+++ b/artfynd/A 1830-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113702608</v>
       </c>
       <c r="B2" t="n">
-        <v>93209</v>
+        <v>93215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1830-2024 artfynd.xlsx
+++ b/artfynd/A 1830-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113702608</v>
       </c>
       <c r="B2" t="n">
-        <v>93215</v>
+        <v>93225</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1830-2024 artfynd.xlsx
+++ b/artfynd/A 1830-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113702608</v>
       </c>
       <c r="B2" t="n">
-        <v>93225</v>
+        <v>93226</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1830-2024 artfynd.xlsx
+++ b/artfynd/A 1830-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113702608</v>
       </c>
       <c r="B2" t="n">
-        <v>93226</v>
+        <v>93227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1830-2024 artfynd.xlsx
+++ b/artfynd/A 1830-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113702608</v>
       </c>
       <c r="B2" t="n">
-        <v>93227</v>
+        <v>93229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1830-2024 artfynd.xlsx
+++ b/artfynd/A 1830-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113702608</v>
       </c>
       <c r="B2" t="n">
-        <v>93229</v>
+        <v>93230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
